--- a/ig/DM-JANVIER-2026/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM-JANVIER-2026/CodeSystem-terminologie-nabm.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3271" uniqueCount="2193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3277" uniqueCount="2197">
   <si>
     <t>Property</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V100</t>
+    <t>V101</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T00:00:00+00:00</t>
+    <t>2026-01-13T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -131,7 +131,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1047</t>
+    <t>1049</t>
   </si>
   <si>
     <t>Code</t>
@@ -720,6 +720,12 @@
   </si>
   <si>
     <t>ELECTROPHORESE DE L'HEMOGLOBINE (GEL POLYACRYLAMIDE)</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>HYBRIDATION SUR PUCE A ADN EN CONTEXTE POST NATAL</t>
   </si>
   <si>
     <t>1246</t>
@@ -6180,6 +6186,12 @@
   </si>
   <si>
     <t>OSTEOCALCINE (SANG)</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>REINTERPRETATION - HYBRIDATION SUR PUCE A ADN EN CONTEXTE POST NATAL</t>
   </si>
   <si>
     <t>1114</t>
@@ -7234,7 +7246,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1048"/>
+  <dimension ref="A1:D1050"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -10717,21 +10729,21 @@
       <c r="C290" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="D290" t="s" s="2">
-        <v>673</v>
-      </c>
+      <c r="D290" s="2"/>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B291" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="C291" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="C291" t="s" s="2">
+      <c r="D291" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="D291" s="2"/>
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
@@ -10911,21 +10923,21 @@
       <c r="C306" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="D306" t="s" s="2">
-        <v>706</v>
-      </c>
+      <c r="D306" s="2"/>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B307" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C307" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="C307" t="s" s="2">
+      <c r="D307" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="D307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
@@ -11081,21 +11093,21 @@
       <c r="C320" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="D320" t="s" s="2">
-        <v>735</v>
-      </c>
+      <c r="D320" s="2"/>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B321" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C321" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="C321" t="s" s="2">
+      <c r="D321" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="D321" s="2"/>
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
@@ -11203,21 +11215,21 @@
       <c r="C330" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="D330" t="s" s="2">
-        <v>756</v>
-      </c>
+      <c r="D330" s="2"/>
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B331" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="C331" t="s" s="2">
         <v>757</v>
       </c>
-      <c r="C331" t="s" s="2">
+      <c r="D331" t="s" s="2">
         <v>758</v>
       </c>
-      <c r="D331" s="2"/>
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
@@ -11325,21 +11337,21 @@
       <c r="C340" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="D340" t="s" s="2">
-        <v>777</v>
-      </c>
+      <c r="D340" s="2"/>
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B341" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="C341" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="C341" t="s" s="2">
+      <c r="D341" t="s" s="2">
         <v>779</v>
       </c>
-      <c r="D341" s="2"/>
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
@@ -11579,21 +11591,21 @@
       <c r="C361" t="s" s="2">
         <v>819</v>
       </c>
-      <c r="D361" t="s" s="2">
-        <v>820</v>
-      </c>
+      <c r="D361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B362" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="C362" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="C362" t="s" s="2">
+      <c r="D362" t="s" s="2">
         <v>822</v>
       </c>
-      <c r="D362" s="2"/>
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
@@ -11821,21 +11833,21 @@
       <c r="C381" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="D381" t="s" s="2">
-        <v>861</v>
-      </c>
+      <c r="D381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B382" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="C382" t="s" s="2">
         <v>862</v>
       </c>
-      <c r="C382" t="s" s="2">
+      <c r="D382" t="s" s="2">
         <v>863</v>
       </c>
-      <c r="D382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
@@ -12646,10 +12658,10 @@
         <v>95</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>10</v>
+        <v>998</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>10</v>
+        <v>999</v>
       </c>
       <c r="D450" s="2"/>
     </row>
@@ -12658,10 +12670,10 @@
         <v>95</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>998</v>
+        <v>10</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>999</v>
+        <v>10</v>
       </c>
       <c r="D451" s="2"/>
     </row>
@@ -13561,7 +13573,7 @@
         <v>1148</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>997</v>
+        <v>1149</v>
       </c>
       <c r="D526" s="2"/>
     </row>
@@ -13570,10 +13582,10 @@
         <v>95</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1150</v>
+        <v>999</v>
       </c>
       <c r="D527" s="2"/>
     </row>
@@ -15181,7 +15193,7 @@
         <v>1417</v>
       </c>
       <c r="C661" t="s" s="2">
-        <v>258</v>
+        <v>1418</v>
       </c>
       <c r="D661" s="2"/>
     </row>
@@ -15190,10 +15202,10 @@
         <v>95</v>
       </c>
       <c r="B662" t="s" s="2">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C662" t="s" s="2">
-        <v>1419</v>
+        <v>260</v>
       </c>
       <c r="D662" s="2"/>
     </row>
@@ -19167,19 +19179,17 @@
       <c r="C993" t="s" s="2">
         <v>2081</v>
       </c>
-      <c r="D993" t="s" s="2">
-        <v>2082</v>
-      </c>
+      <c r="D993" s="2"/>
     </row>
     <row r="994">
       <c r="A994" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B994" t="s" s="2">
+        <v>2082</v>
+      </c>
+      <c r="C994" t="s" s="2">
         <v>2083</v>
-      </c>
-      <c r="C994" t="s" s="2">
-        <v>2084</v>
       </c>
       <c r="D994" s="2"/>
     </row>
@@ -19188,12 +19198,14 @@
         <v>95</v>
       </c>
       <c r="B995" t="s" s="2">
+        <v>2084</v>
+      </c>
+      <c r="C995" t="s" s="2">
         <v>2085</v>
       </c>
-      <c r="C995" t="s" s="2">
+      <c r="D995" t="s" s="2">
         <v>2086</v>
       </c>
-      <c r="D995" s="2"/>
     </row>
     <row r="996">
       <c r="A996" t="s" s="2">
@@ -19275,7 +19287,7 @@
         <v>2099</v>
       </c>
       <c r="C1002" t="s" s="2">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="D1002" s="2"/>
     </row>
@@ -19284,10 +19296,10 @@
         <v>95</v>
       </c>
       <c r="B1003" t="s" s="2">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="C1003" t="s" s="2">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="D1003" s="2"/>
     </row>
@@ -19296,7 +19308,7 @@
         <v>95</v>
       </c>
       <c r="B1004" t="s" s="2">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="C1004" t="s" s="2">
         <v>2103</v>
@@ -19325,19 +19337,17 @@
       <c r="C1006" t="s" s="2">
         <v>2107</v>
       </c>
-      <c r="D1006" t="s" s="2">
-        <v>2108</v>
-      </c>
+      <c r="D1006" s="2"/>
     </row>
     <row r="1007">
       <c r="A1007" t="s" s="2">
         <v>95</v>
       </c>
       <c r="B1007" t="s" s="2">
+        <v>2108</v>
+      </c>
+      <c r="C1007" t="s" s="2">
         <v>2109</v>
-      </c>
-      <c r="C1007" t="s" s="2">
-        <v>2110</v>
       </c>
       <c r="D1007" s="2"/>
     </row>
@@ -19346,12 +19356,14 @@
         <v>95</v>
       </c>
       <c r="B1008" t="s" s="2">
+        <v>2110</v>
+      </c>
+      <c r="C1008" t="s" s="2">
         <v>2111</v>
       </c>
-      <c r="C1008" t="s" s="2">
+      <c r="D1008" t="s" s="2">
         <v>2112</v>
       </c>
-      <c r="D1008" s="2"/>
     </row>
     <row r="1009">
       <c r="A1009" t="s" s="2">
@@ -19832,6 +19844,30 @@
         <v>2192</v>
       </c>
       <c r="D1048" s="2"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B1049" t="s" s="2">
+        <v>2193</v>
+      </c>
+      <c r="C1049" t="s" s="2">
+        <v>2194</v>
+      </c>
+      <c r="D1049" s="2"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B1050" t="s" s="2">
+        <v>2195</v>
+      </c>
+      <c r="C1050" t="s" s="2">
+        <v>2196</v>
+      </c>
+      <c r="D1050" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
